--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.24</v>
+        <v>2.23</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,65 +3632,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X25" t="n">
         <v>3.1</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.9</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N27" t="n">
-        <v>2.23</v>
+        <v>3.24</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,19 +3961,406 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3" t="n">
+        <v>45958.69791666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Republic of Ireland Premier Division</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cobh Ramblers</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3" t="n">
+        <v>45958.69791666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>45958.82291666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.05</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="N24" t="n">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,65 +3632,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.24</v>
+        <v>2.36</v>
       </c>
       <c r="O27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S27" t="n">
         <v>2.65</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="M30" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O29" t="n">
         <v>2.75</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="N25" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3761,65 +3761,65 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X26" t="n">
         <v>3.3</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Y26" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AD26" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.1</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="M6" t="n">
         <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.24</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.02</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>2.33</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.03</v>
+        <v>2.65</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.33</v>
+        <v>1.56</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="M21" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.85</v>
+        <v>1.37</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>7.2</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.3</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Y29" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Z29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK30"/>
+  <dimension ref="A1:AK31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>3.65</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,14 +1701,14 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.4</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.02</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
         <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
         <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.45</v>
+        <v>2.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N14" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,16 +2385,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
         <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>7.2</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4361,6 +4361,135 @@
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.82291666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3" t="n">
+        <v>45958.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="M10" t="n">
         <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.33</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>6.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>2.34</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2391,10 +2391,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.4</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.56</v>
+        <v>2.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X25" t="n">
         <v>3.3</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.1</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4019,65 +4019,65 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="M29" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.24</v>
+        <v>2.51</v>
       </c>
       <c r="O29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4290,34 +4290,34 @@
         <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y30" t="n">
         <v>1.65</v>
@@ -4326,16 +4326,16 @@
         <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
         <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.37</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.07</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>6.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>4.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>2.85</v>
       </c>
       <c r="M14" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>6.3</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2262,10 +2262,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N15" t="n">
         <v>2.8</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.34</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.4</v>
+        <v>1.56</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
         <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>2.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="N25" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
         <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.8</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.34</v>
+        <v>9</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>7.2</v>
+        <v>4.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>2.07</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,14 +2991,14 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N20" t="n">
         <v>3.4</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.02</v>
-      </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>2.36</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>2.89</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45958.69791666666</v>
+        <v>45958.82291666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,135 +4360,6 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45958.82291666666</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>45958</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Portimonense</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="3" t="n">
         <v>45958.875</v>
       </c>
     </row>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>6.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>2.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
         <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>2.07</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>5.6</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.24</v>
+        <v>2.36</v>
       </c>
       <c r="O24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.65</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.3</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
         <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45958.82291666666</v>
+        <v>45958.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45958.875</v>
+        <v>45958.82291666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>2.95</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>3.65</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,49 +2604,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.05</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>6.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X24" t="n">
         <v>3.3</v>
       </c>
-      <c r="N24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="M26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3.3</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2.4</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,14 +2604,14 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N17" t="n">
         <v>2.4</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.95</v>
-      </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.87</v>
+        <v>2.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.24</v>
+        <v>2.51</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="M25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X25" t="n">
         <v>3.3</v>
       </c>
-      <c r="N25" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>6.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.7</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M9" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.85</v>
+        <v>2.07</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,14 +2733,14 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N18" t="n">
         <v>3.4</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.87</v>
+        <v>2.85</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>5.6</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>2.43</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3890,65 +3890,65 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA27" t="n">
         <v>2.9</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.55</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>6.3</v>
+        <v>3.65</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
         <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.05</v>
+        <v>9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="N24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O24" t="n">
         <v>2.65</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.55</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,65 +3632,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.24</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.65</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
         <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>1.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="M14" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>2.05</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
         <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>2.95</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,49 +3120,49 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
         <v>2.05</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>6.3</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3632,65 +3632,65 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3.3</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="M29" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.1</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.8</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,49 +1443,49 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2.07</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.92</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N10" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,16 +1869,16 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.85</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>6.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
         <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
         <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="M17" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X26" t="n">
         <v>3.3</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.24</v>
+        <v>2.51</v>
       </c>
       <c r="O28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4148,65 +4148,65 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK30"/>
+  <dimension ref="A1:AK29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,49 +1443,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2.05</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>4.05</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6.3</v>
+        <v>2.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
         <v>2.4</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
         <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>6.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3503,65 +3503,65 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.43</v>
+        <v>2.72</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>2.65</v>
@@ -3804,10 +3804,10 @@
         <v>3.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
         <v>3.2</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,135 +4231,6 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45958.69791666666</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>45958</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" s="3" t="n">
         <v>45958.82291666666</v>
       </c>
     </row>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK29"/>
+  <dimension ref="A1:AK31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1194,34 +1194,34 @@
         <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y6" t="n">
         <v>1.98</v>
@@ -1230,16 +1230,16 @@
         <v>1.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S8" t="n">
         <v>3.4</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1581,34 +1581,34 @@
         <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y9" t="n">
         <v>1.97</v>
@@ -1617,16 +1617,16 @@
         <v>1.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
         <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
         <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,62 +2217,62 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.4</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.77</v>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.87</v>
+        <v>2.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,34 +2484,34 @@
         <v>3.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y16" t="n">
         <v>1.92</v>
@@ -2520,16 +2520,16 @@
         <v>1.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O18" t="n">
         <v>2.75</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.55</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>6.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>2.51</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>6.3</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>9</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
         <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
         <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
         <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,85 +4152,343 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.85</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.45</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
         <v>1.05</v>
       </c>
       <c r="W29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK29" s="3" t="n">
+        <v>45958.69791666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Northern Ireland NIFL Premiership</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Coleraine</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Linfield</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3" t="n">
+        <v>45958.69791666666</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.25</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="AH31" t="n">
         <v>1.55</v>
       </c>
-      <c r="AD29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="n">
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3" t="n">
         <v>45958.82291666666</v>
       </c>
     </row>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>3.86</v>
+        <v>3.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>5.6</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.18</v>
+        <v>3.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,62 +1572,62 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>3.46</v>
       </c>
       <c r="P9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.43</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.56</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>3.35</v>
+        <v>3.86</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.12</v>
+        <v>2.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="M12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X12" t="n">
         <v>3.4</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.99</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>1.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>4.05</v>
       </c>
       <c r="O13" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S13" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
         <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="P14" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.25</v>
+        <v>5.18</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA15" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AB15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.27</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.29</v>
       </c>
-      <c r="X16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AC16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.92</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.56</v>
+        <v>4.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.22</v>
+        <v>2.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>2.07</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="T18" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.3</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.98</v>
+        <v>3.44</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
         <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="P19" t="n">
         <v>2.05</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X19" t="n">
         <v>3</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.99</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="M20" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.69</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>3.58</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.67</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>3.98</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.69</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y21" t="n">
         <v>2.4</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="Z21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC21" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
-        <v>4.05</v>
+        <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="P22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.89</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>3.12</v>
+        <v>5.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.9</v>
+        <v>2.51</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.86</v>
+        <v>2.69</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>9</v>
       </c>
       <c r="O23" t="n">
-        <v>4.15</v>
+        <v>1.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>6.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>3.04</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.4</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.95</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC25" t="n">
         <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="O27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
         <v>3</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.96</v>
-      </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X27" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1194,19 +1194,19 @@
         <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
         <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
         <v>3</v>
@@ -1230,13 +1230,13 @@
         <v>1.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.65</v>
+        <v>3.44</v>
       </c>
       <c r="AB6" t="n">
         <v>1.26</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
         <v>1.64</v>
@@ -1323,19 +1323,19 @@
         <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
         <v>2.75</v>
@@ -1350,7 +1350,7 @@
         <v>1.3</v>
       </c>
       <c r="X7" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="Y7" t="n">
         <v>2.02</v>
@@ -1359,16 +1359,16 @@
         <v>1.78</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AB7" t="n">
         <v>1.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.85</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA9" t="n">
         <v>3.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.12</v>
       </c>
       <c r="AB9" t="n">
         <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
         <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>2.99</v>
+        <v>3.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1842,10 +1842,10 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
@@ -1866,7 +1866,7 @@
         <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="Y11" t="n">
         <v>1.72</v>
@@ -1878,7 +1878,7 @@
         <v>2.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC11" t="n">
         <v>1.56</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2.07</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Z12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA12" t="n">
         <v>3.55</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="AB12" t="n">
         <v>1.29</v>
       </c>
-      <c r="X12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC12" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.39</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.37</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AA13" t="n">
         <v>3.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.07</v>
+        <v>2.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.18</v>
+        <v>3.84</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.34</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.48</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,62 +2346,62 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.22</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X15" t="n">
         <v>2.89</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.38</v>
-      </c>
       <c r="Y15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2</v>
-      </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S16" t="n">
         <v>3.4</v>
       </c>
-      <c r="N16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.69</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>2.34</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
         <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>2.99</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="N17" t="n">
-        <v>2.05</v>
+        <v>3.13</v>
       </c>
       <c r="O17" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.7</v>
+        <v>3.89</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="X17" t="n">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>3.88</v>
       </c>
       <c r="R18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD18" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,43 +2862,43 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
         <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.01</v>
+        <v>3.12</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
         <v>3.64</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
         <v>2.05</v>
@@ -2907,16 +2907,16 @@
         <v>1.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="X20" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="P21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.56</v>
+        <v>2.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3258,13 +3258,13 @@
         <v>6.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="R22" t="n">
         <v>1.22</v>
@@ -3276,19 +3276,19 @@
         <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X22" t="n">
         <v>5.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
         <v>2.51</v>
@@ -3300,7 +3300,7 @@
         <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
         <v>2.13</v>
@@ -3319,7 +3319,7 @@
         <v>1.16</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.35</v>
       </c>
-      <c r="M23" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="V23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.8</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.62</v>
+        <v>3.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.04</v>
+        <v>1.27</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.96</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.18</v>
+        <v>2.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.82</v>
+        <v>2.51</v>
       </c>
       <c r="O27" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
         <v>3.02</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
         <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
         <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U30" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
         <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AA30" t="n">
         <v>3.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,77 +1314,77 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="O7" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.38</v>
+        <v>2.61</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.27</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA8" t="n">
         <v>3</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.52</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA9" t="n">
         <v>4</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
         <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.77</v>
+        <v>3.22</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.12</v>
+        <v>3.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.15</v>
+        <v>2.53</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.61</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="M12" t="n">
         <v>3.5</v>
       </c>
       <c r="N12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.05</v>
       </c>
-      <c r="O12" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>3.24</v>
+        <v>2.77</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
         <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.55</v>
+        <v>3.12</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,58 +2088,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.08</v>
+        <v>2.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.66</v>
+        <v>3.64</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD13" t="n">
         <v>1.94</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.92</v>
+        <v>1.87</v>
       </c>
       <c r="P14" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.84</v>
+        <v>6.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.36</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.72</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>5.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>3.58</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.7</v>
       </c>
       <c r="V15" t="n">
         <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>2.89</v>
+        <v>5.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>1.45</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>2.51</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>2.8</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.18</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>2.72</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>2.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.64</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.13</v>
+        <v>2.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.89</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
         <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2.95</v>
+        <v>4.54</v>
       </c>
       <c r="P18" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.88</v>
+        <v>2.68</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.24</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>3.12</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
         <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,31 +2991,31 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.16</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T20" t="n">
-        <v>2.63</v>
+        <v>2.77</v>
       </c>
       <c r="U20" t="n">
         <v>1.39</v>
@@ -3024,28 +3024,28 @@
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.25</v>
+        <v>5.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>1.88</v>
+        <v>3.12</v>
       </c>
       <c r="P22" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.74</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>3.58</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U22" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>5.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.51</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>3.84</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X23" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="Z23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="P29" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="P31" t="n">
         <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T31" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="U31" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V31" t="n">
         <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
         <v>4.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AB31" t="n">
         <v>1.46</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -822,37 +822,37 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -951,37 +951,37 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1197,16 +1197,16 @@
         <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
         <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="T6" t="n">
         <v>3</v>
@@ -1218,10 +1218,10 @@
         <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="Y6" t="n">
         <v>1.98</v>
@@ -1233,13 +1233,13 @@
         <v>3.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,62 +1314,62 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.65</v>
+        <v>3.13</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.12</v>
+        <v>3.89</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="X7" t="n">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="Y7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>2.54</v>
+        <v>2.72</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
         <v>1.32</v>
       </c>
       <c r="X10" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="M11" t="n">
         <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>3.64</v>
       </c>
       <c r="P11" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
         <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.77</v>
       </c>
-      <c r="AA11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.4</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.38</v>
+        <v>2.48</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2346,22 +2346,22 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="M15" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="P15" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.74</v>
+        <v>5.28</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
@@ -2373,22 +2373,22 @@
         <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>5.15</v>
+        <v>5.48</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AA15" t="n">
         <v>2.15</v>
@@ -2400,7 +2400,7 @@
         <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>2.72</v>
+        <v>3.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.07</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>2.66</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="N18" t="n">
-        <v>2.05</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>4.54</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>3.24</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
         <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="Z18" t="n">
         <v>1.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
-        <v>2.66</v>
+        <v>4.54</v>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.77</v>
+        <v>3.24</v>
       </c>
       <c r="U20" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.29</v>
       </c>
-      <c r="X20" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.86</v>
       </c>
-      <c r="AA20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>5.6</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.18</v>
+        <v>3.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="M22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.4</v>
       </c>
-      <c r="N22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.12</v>
-      </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
         <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="O24" t="n">
-        <v>2.67</v>
+        <v>3.24</v>
       </c>
       <c r="P24" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.96</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,55 +804,55 @@
         <v>3.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AA3" t="n">
         <v>2.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
         <v>1.64</v>
@@ -1197,19 +1197,19 @@
         <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U6" t="n">
         <v>1.38</v>
@@ -1221,7 +1221,7 @@
         <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Y6" t="n">
         <v>1.98</v>
@@ -1230,13 +1230,13 @@
         <v>1.77</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
         <v>1.66</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="N7" t="n">
-        <v>3.13</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.89</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>3.51</v>
       </c>
       <c r="O8" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.16</v>
+        <v>3.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.89</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
         <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="M9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>3.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="M10" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.4</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>3.1</v>
+        <v>5.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.95</v>
+        <v>1.54</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.64</v>
+        <v>1.85</v>
       </c>
       <c r="P11" t="n">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>5.13</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.38</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.85</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.4</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.77</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>2.92</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>2.07</v>
+        <v>3.64</v>
       </c>
       <c r="P13" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.18</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="T13" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.48</v>
+        <v>3.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>3.06</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>2.79</v>
       </c>
       <c r="O14" t="n">
-        <v>1.87</v>
+        <v>3.12</v>
       </c>
       <c r="P14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.25</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X14" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.54</v>
+        <v>3.47</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.99</v>
+        <v>3.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.28</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>5.48</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.48</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>3.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.47</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="O16" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
         <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
         <v>1.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.08</v>
+        <v>3.97</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.38</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.29</v>
       </c>
-      <c r="X17" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z18" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>4</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AA18" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.28</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="N19" t="n">
-        <v>2.07</v>
+        <v>3.74</v>
       </c>
       <c r="O19" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
-        <v>4.54</v>
+        <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>3.8</v>
       </c>
       <c r="R20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
         <v>1.42</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X20" t="n">
-        <v>3.01</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.41</v>
       </c>
       <c r="O21" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="R21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.42</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="X21" t="n">
         <v>2.8</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.72</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>3.01</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>3.22</v>
+        <v>2.97</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.77</v>
+        <v>3.12</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
@@ -3660,59 +3660,59 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="O31" t="n">
         <v>2.9</v>
@@ -4428,16 +4428,16 @@
         <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V31" t="n">
         <v>1.03</v>
@@ -4446,25 +4446,25 @@
         <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AA31" t="n">
         <v>2.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4490,6 +4490,135 @@
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.82291666666</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="n">
+        <v>45958.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK32"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,13 +807,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="R3" t="n">
         <v>1.22</v>
@@ -825,7 +825,7 @@
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -852,7 +852,7 @@
         <v>1.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
         <v>1.64</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.7</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>5.15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.46</v>
+        <v>7.95</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>1.72</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>7.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45958.60416666666</v>
+        <v>45958.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.75</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.19</v>
+        <v>4.19</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="O7" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.01</v>
+        <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>2.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45958.6875</v>
+        <v>45958.60416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,62 +1443,62 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.1</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>2.54</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>2.99</v>
+        <v>3.95</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.38</v>
+        <v>2.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
-        <v>3.59</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.16</v>
       </c>
-      <c r="X10" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.79</v>
       </c>
       <c r="O11" t="n">
-        <v>1.85</v>
+        <v>3.12</v>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.13</v>
+        <v>3.35</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>1.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.25</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.8</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
         <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.3</v>
       </c>
-      <c r="X13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="M14" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.79</v>
+        <v>2.17</v>
       </c>
       <c r="O14" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
         <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.47</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>1.9</v>
+        <v>3.41</v>
       </c>
       <c r="O15" t="n">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.6</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.42</v>
       </c>
-      <c r="S15" t="n">
+      <c r="X15" t="n">
         <v>2.8</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.1</v>
-      </c>
       <c r="Y15" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2.89</v>
+        <v>3.59</v>
       </c>
       <c r="N16" t="n">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>5.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.97</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>2.67</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.65</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.42</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.3</v>
       </c>
-      <c r="X17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.15</v>
       </c>
-      <c r="M18" t="n">
+      <c r="Q18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="Y18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA18" t="n">
         <v>3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="AB18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>3.97</v>
       </c>
       <c r="M21" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3.41</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
         <v>1.85</v>
@@ -3190,7 +3190,7 @@
         <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.88</v>
       </c>
-      <c r="T22" t="n">
-        <v>2.97</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
         <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.35</v>
+        <v>2.99</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45958.69791666666</v>
+        <v>45958.6875</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>2.82</v>
       </c>
       <c r="O25" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
         <v>1.33</v>
@@ -3660,59 +3660,59 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.57</v>
+        <v>2.64</v>
       </c>
       <c r="O26" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.22</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
         <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="O31" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X31" t="n">
-        <v>4.35</v>
+        <v>3.22</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.65</v>
+        <v>1.96</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45958.82291666666</v>
+        <v>45958.69791666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,126 +4498,255 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3" t="n">
+        <v>45958.82291666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Portugal LigaPro</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Portimonense</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="3" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
         <v>45958.875</v>
       </c>
     </row>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>5.15</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="O7" t="n">
         <v>7</v>
@@ -1329,13 +1329,13 @@
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
         <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T7" t="n">
         <v>3.08</v>
@@ -1356,16 +1356,16 @@
         <v>2.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AB7" t="n">
         <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="AD7" t="n">
         <v>1.66</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>1.85</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.13</v>
+        <v>3.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="X8" t="n">
-        <v>5.25</v>
+        <v>3.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="O9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.64</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,62 +1701,62 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.85</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.3</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.47</v>
+        <v>2.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="N12" t="n">
-        <v>1.9</v>
+        <v>2.51</v>
       </c>
       <c r="O12" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
         <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="U12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.38</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X12" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Z12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA12" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2097,10 +2097,10 @@
         <v>2.31</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
         <v>2.98</v>
@@ -2109,16 +2109,16 @@
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
         <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
         <v>1.25</v>
@@ -2139,7 +2139,7 @@
         <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AD13" t="n">
         <v>2</v>
@@ -2158,7 +2158,7 @@
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.92</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.17</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.64</v>
+        <v>1.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.44</v>
+        <v>2.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>3.97</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="N15" t="n">
-        <v>3.41</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>4.64</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.85</v>
+        <v>2.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>3.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.29</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.1</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.89</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>3.4</v>
+        <v>5.15</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.92</v>
+        <v>1.45</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.88</v>
+        <v>2.48</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.92</v>
+        <v>2.21</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="N18" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>3.16</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.88</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.97</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,62 +2862,62 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
         <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.3</v>
       </c>
-      <c r="X19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AC19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,49 +2991,49 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S20" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
         <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
         <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
         <v>4</v>
@@ -3045,7 +3045,7 @@
         <v>2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,58 +3120,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.97</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>2.52</v>
       </c>
       <c r="P21" t="n">
         <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.65</v>
+        <v>4.74</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.87</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
         <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AD21" t="n">
         <v>1.85</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>4.24</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.55</v>
+        <v>2.61</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.38</v>
+        <v>4.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.36</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.45</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="O26" t="n">
-        <v>3.24</v>
+        <v>2.69</v>
       </c>
       <c r="P26" t="n">
         <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
         <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AJ26" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="O29" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="P29" t="n">
         <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U29" t="n">
         <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
         <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4557,22 +4557,22 @@
         <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
         <v>2.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V32" t="n">
         <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
         <v>4.35</v>
@@ -4590,10 +4590,10 @@
         <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M8" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="N8" t="n">
-        <v>2.79</v>
+        <v>3.01</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.36</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X8" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>3.16</v>
       </c>
       <c r="N9" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.17</v>
+        <v>3.84</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W9" t="n">
         <v>1.38</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.31</v>
-      </c>
       <c r="X9" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
         <v>1.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
         <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>3.59</v>
+        <v>4.54</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>5.27</v>
       </c>
       <c r="O11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.1</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>5.04</v>
+        <v>5.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
         <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
         <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>3.27</v>
+        <v>2.94</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.03</v>
+        <v>3.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="O13" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="P13" t="n">
         <v>2.09</v>
@@ -2118,7 +2118,7 @@
         <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>1.25</v>
@@ -2127,10 +2127,10 @@
         <v>3.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AA13" t="n">
         <v>3.12</v>
@@ -2139,7 +2139,7 @@
         <v>1.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AD13" t="n">
         <v>2</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.85</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.78</v>
+        <v>2.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.97</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>4.78</v>
       </c>
       <c r="O15" t="n">
-        <v>4.64</v>
+        <v>2.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.26</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="X15" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.55</v>
+        <v>2.48</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.47</v>
+        <v>3.59</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
         <v>1.9</v>
@@ -2487,7 +2487,7 @@
         <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q16" t="n">
         <v>2.6</v>
@@ -2499,10 +2499,10 @@
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
         <v>1.07</v>
@@ -2514,10 +2514,10 @@
         <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
         <v>3.44</v>
@@ -2526,7 +2526,7 @@
         <v>1.26</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AD16" t="n">
         <v>1.83</v>
@@ -2545,7 +2545,7 @@
         <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.44</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q17" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.21</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.45</v>
+        <v>2.93</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>2.72</v>
       </c>
       <c r="M18" t="n">
-        <v>2.89</v>
+        <v>3.26</v>
       </c>
       <c r="N18" t="n">
-        <v>2.91</v>
+        <v>2.51</v>
       </c>
       <c r="O18" t="n">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>3.27</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.55</v>
+        <v>4.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
         <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.1</v>
+        <v>3.97</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.69</v>
+        <v>4.64</v>
       </c>
       <c r="P19" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>2.94</v>
+        <v>3.26</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.29</v>
       </c>
-      <c r="X19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.03</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X20" t="n">
-        <v>2.67</v>
+        <v>2.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>2.81</v>
       </c>
       <c r="O21" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.74</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>2.99</v>
+        <v>4.24</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
       </c>
       <c r="P22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="X22" t="n">
-        <v>4.24</v>
+        <v>2.67</v>
       </c>
       <c r="Y22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.22</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>4.74</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="N24" t="n">
-        <v>2.17</v>
+        <v>3.22</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.94</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="O26" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="O28" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="P29" t="n">
         <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
         <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
         <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AJ29" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="O32" t="n">
         <v>2.9</v>
@@ -4557,10 +4557,10 @@
         <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
         <v>2.4</v>
@@ -4575,25 +4575,25 @@
         <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>4.35</v>
+        <v>3.92</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AA32" t="n">
         <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45958.41666666666</v>
+        <v>45958.375</v>
       </c>
     </row>
     <row r="4">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45958.45833333334</v>
+        <v>45958.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
         <v>1.46</v>
@@ -1329,34 +1329,34 @@
         <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="T7" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA7" t="n">
         <v>3.7</v>
@@ -1365,10 +1365,10 @@
         <v>1.24</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.38</v>
+        <v>3.47</v>
       </c>
       <c r="M8" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.14</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>3.97</v>
       </c>
       <c r="M9" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.92</v>
+        <v>4.64</v>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.84</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>3.26</v>
       </c>
       <c r="U9" t="n">
         <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.26</v>
+        <v>2.89</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="O10" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.33</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>2.72</v>
       </c>
       <c r="M11" t="n">
-        <v>4.54</v>
+        <v>3.26</v>
       </c>
       <c r="N11" t="n">
-        <v>5.27</v>
+        <v>2.51</v>
       </c>
       <c r="O11" t="n">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q11" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>3.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>5.15</v>
+        <v>2.89</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.48</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.38</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.69</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="N13" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="O13" t="n">
-        <v>3.53</v>
+        <v>3.19</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.98</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X13" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.82</v>
       </c>
-      <c r="AA13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>3.53</v>
       </c>
       <c r="P14" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="AB14" t="n">
         <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.78</v>
+        <v>6.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="P15" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.59</v>
+        <v>1.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.59</v>
+        <v>2.09</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N16" t="n">
-        <v>1.9</v>
+        <v>3.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.6</v>
+        <v>4.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="T16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="Z16" t="n">
         <v>1.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.88</v>
+        <v>2.52</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.25</v>
+        <v>4.74</v>
       </c>
       <c r="R17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.32</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.93</v>
+        <v>1.82</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.03</v>
+        <v>4.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.97</v>
+        <v>1.54</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>4.64</v>
+        <v>2.03</v>
       </c>
       <c r="P19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.84</v>
+        <v>2.35</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>2.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
         <v>2.2</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>4.72</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="X21" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="P22" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.03</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.54</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.51</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>2.35</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>2.99</v>
+        <v>4.24</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
       <c r="M24" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.22</v>
+        <v>2.17</v>
       </c>
       <c r="O24" t="n">
-        <v>2.68</v>
+        <v>3.86</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.07</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AA24" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="Z26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="O29" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
         <v>3.3</v>
       </c>
       <c r="R29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.33</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z29" t="n">
+      <c r="AH29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.7</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X30" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
         <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O32" t="n">
         <v>2.76</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.9</v>
       </c>
       <c r="P32" t="n">
         <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R32" t="n">
         <v>1.29</v>
@@ -4566,10 +4566,10 @@
         <v>2.4</v>
       </c>
       <c r="U32" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
         <v>1.18</v>
@@ -4581,7 +4581,7 @@
         <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AA32" t="n">
         <v>2.75</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>5.15</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>7.95</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.72</v>
@@ -1326,22 +1326,22 @@
         <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
@@ -1350,7 +1350,7 @@
         <v>1.35</v>
       </c>
       <c r="X7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Y7" t="n">
         <v>1.98</v>
@@ -1359,10 +1359,10 @@
         <v>1.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
         <v>2.25</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.47</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X8" t="n">
         <v>3.3</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.94</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.97</v>
+        <v>1.54</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.64</v>
+        <v>1.99</v>
       </c>
       <c r="P9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.91</v>
+        <v>3.51</v>
       </c>
       <c r="O10" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
         <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AC10" t="n">
         <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="M11" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T11" t="n">
-        <v>3.27</v>
+        <v>2.94</v>
       </c>
       <c r="U11" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.03</v>
+        <v>3.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC11" t="n">
         <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,62 +1959,62 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>2.79</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,43 +2088,43 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="M13" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="N13" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="O13" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>3.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
         <v>2.88</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
         <v>2.05</v>
@@ -2133,16 +2133,16 @@
         <v>1.77</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB13" t="n">
         <v>1.29</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.53</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.98</v>
+        <v>2.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
         <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>3.19</v>
       </c>
       <c r="N15" t="n">
-        <v>6.4</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
-        <v>1.99</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.64</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.62</v>
+        <v>4.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.58</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23</v>
+        <v>3.59</v>
       </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.06</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>3.12</v>
+        <v>4.55</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.85</v>
+        <v>2.53</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>3.01</v>
       </c>
       <c r="O17" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.74</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.62</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.99</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.22</v>
+        <v>3.97</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.54</v>
+        <v>2.03</v>
       </c>
       <c r="M19" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
         <v>4</v>
       </c>
-      <c r="N19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.02</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>5.56</v>
+        <v>3.15</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.57</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.4</v>
       </c>
-      <c r="O20" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.6</v>
+        <v>2.92</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>2.17</v>
       </c>
       <c r="O21" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.72</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>4.55</v>
+        <v>3.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>3.44</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N22" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AB22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.3</v>
       </c>
-      <c r="X22" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,62 +3378,62 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>6.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="N24" t="n">
-        <v>2.17</v>
+        <v>3.41</v>
       </c>
       <c r="O24" t="n">
-        <v>3.86</v>
+        <v>2.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.99</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="AB24" t="n">
         <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
         <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
         <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
         <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AB26" t="n">
         <v>1.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.72</v>
+        <v>2.19</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2.51</v>
+        <v>2.84</v>
       </c>
       <c r="O31" t="n">
-        <v>3.24</v>
+        <v>2.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X31" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z31" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AA31" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="M32" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="O32" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="P32" t="n">
         <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AA32" t="n">
         <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="N8" t="n">
-        <v>2.31</v>
+        <v>3.01</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.98</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.12</v>
+        <v>4.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.08</v>
+        <v>3.85</v>
       </c>
       <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.22</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC9" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,58 +1701,58 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.51</v>
+        <v>2.31</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>2.98</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
         <v>2</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.18</v>
+        <v>3.97</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
         <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,43 +1959,43 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="N12" t="n">
-        <v>2.79</v>
+        <v>2.91</v>
       </c>
       <c r="O12" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
         <v>2.05</v>
@@ -2004,17 +2004,17 @@
         <v>1.77</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
         <v>1.29</v>
       </c>
       <c r="AC12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.91</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>3.51</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
       </c>
       <c r="V14" t="n">
         <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>3.47</v>
       </c>
       <c r="M15" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="X15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>3.59</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA17" t="n">
         <v>3.3</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.65</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
         <v>1.6</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.97</v>
+        <v>1.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.59</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="X18" t="n">
-        <v>3.2</v>
+        <v>4.55</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2.15</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.56</v>
+        <v>2.88</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.23</v>
+        <v>3.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>2.79</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>3.19</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>3.23</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>3.01</v>
       </c>
       <c r="O23" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.78</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="N24" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="AB24" t="n">
         <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,40 +3636,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="M25" t="n">
         <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="O25" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
         <v>3.45</v>
@@ -3681,16 +3681,16 @@
         <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
         <v>1.75</v>
@@ -1341,7 +1341,7 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
@@ -1362,7 +1362,7 @@
         <v>3.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
         <v>2.25</v>
@@ -1387,10 +1387,10 @@
         <v>1.11</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45958.60416666666</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3.01</v>
+        <v>3.51</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
         <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1590,7 +1590,7 @@
         <v>3.85</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
         <v>2.47</v>
@@ -1599,16 +1599,16 @@
         <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V9" t="n">
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y9" t="n">
         <v>2.2</v>
@@ -1620,7 +1620,7 @@
         <v>3.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
         <v>1.92</v>
@@ -1645,10 +1645,10 @@
         <v>1.65</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.31</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.98</v>
+        <v>5.08</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.97</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
         <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
         <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="M12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.89</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA12" t="n">
         <v>3</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.3</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X13" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.6</v>
+        <v>3.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>3.51</v>
+        <v>3.74</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
         <v>3.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.47</v>
+        <v>2.53</v>
       </c>
       <c r="M15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.3</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.42</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="X15" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.54</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2484,7 +2484,7 @@
         <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
         <v>2.47</v>
@@ -2496,13 +2496,13 @@
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
         <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -2526,10 +2526,10 @@
         <v>1.34</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.05</v>
+        <v>3.59</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.84</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.94</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>2.99</v>
+        <v>4.55</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.59</v>
+        <v>2.89</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="O18" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.03</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>3.74</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.38</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         <v>1.28</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>2.79</v>
       </c>
       <c r="O20" t="n">
-        <v>1.99</v>
+        <v>3.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.08</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,13 +3190,13 @@
         <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>3.97</v>
       </c>
       <c r="M22" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
         <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AB22" t="n">
         <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>3.01</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.36</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
         <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>3</v>
+        <v>4.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>3.47</v>
       </c>
       <c r="M24" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.9</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Y24" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.03</v>
+        <v>3.54</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,40 +3636,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="M25" t="n">
         <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>2.57</v>
       </c>
       <c r="O25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.65</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X25" t="n">
         <v>3.45</v>
@@ -3681,16 +3681,16 @@
         <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3777,22 +3777,22 @@
         <v>2.97</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -3801,7 +3801,7 @@
         <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="Y26" t="n">
         <v>1.8</v>
@@ -3813,7 +3813,7 @@
         <v>2.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
         <v>1.67</v>
@@ -3835,13 +3835,13 @@
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4548,34 +4548,34 @@
         <v>2.54</v>
       </c>
       <c r="O32" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P32" t="n">
         <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
         <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X32" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Y32" t="n">
         <v>1.65</v>
@@ -4587,7 +4587,7 @@
         <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
         <v>1.55</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45958.375</v>
+        <v>45958.41666666666</v>
       </c>
     </row>
     <row r="4">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45958.41666666666</v>
+        <v>45958.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>7.39</v>
       </c>
       <c r="O6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y6" t="n">
         <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI6" t="n">
         <v>1.33</v>
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
         <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X7" t="n">
         <v>3.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AA7" t="n">
         <v>3.5</v>
@@ -1365,10 +1365,10 @@
         <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.51</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
         <v>2.62</v>
       </c>
       <c r="T8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X8" t="n">
         <v>3</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
         <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>2.9</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>2.13</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.08</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.62</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.62</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.98</v>
+        <v>3.22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,13 +1900,13 @@
         <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.09</v>
+        <v>1.68</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.01</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="M13" t="n">
         <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
         <v>3</v>
       </c>
       <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.35</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>3.73</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="N14" t="n">
-        <v>3.74</v>
+        <v>1.97</v>
       </c>
       <c r="O14" t="n">
-        <v>2.57</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
         <v>1.43</v>
@@ -2244,28 +2244,28 @@
         <v>2.99</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X14" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" t="n">
         <v>1.85</v>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.65</v>
+        <v>2.38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.01</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AI15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.95</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AD16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD16" t="n">
+      <c r="AH16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="M17" t="n">
-        <v>3.59</v>
+        <v>3.01</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="X17" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.3</v>
+        <v>1.56</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.33</v>
+        <v>3.9</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AI17" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.91</v>
+        <v>5.4</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>5.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.77</v>
+        <v>2.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>4.23</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.37</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.32</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.77</v>
+        <v>3.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,58 +2991,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M20" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.79</v>
+        <v>2.58</v>
       </c>
       <c r="O20" t="n">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.4</v>
+        <v>4.29</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
         <v>1.85</v>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="T21" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.97</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.62</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.3</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>3.15</v>
+        <v>3.82</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>1.72</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.03</v>
+        <v>2.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.47</v>
+        <v>1.34</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.9</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>1.94</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>6.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.62</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="AB24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI24" t="n">
         <v>1.34</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>1.78</v>
+        <v>3.6</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N26" t="n">
         <v>3.3</v>
       </c>
-      <c r="N26" t="n">
-        <v>2.51</v>
-      </c>
       <c r="O26" t="n">
-        <v>2.97</v>
+        <v>2.6</v>
       </c>
       <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3.6</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="M30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
         <v>3.21</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.9</v>
-      </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4619,135 +4619,6 @@
       </c>
       <c r="AK32" s="3" t="n">
         <v>45958.82291666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45958</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Felgueiras 1932</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Farense</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="n">
-        <v>45958.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK32"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="M2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N2" t="n">
         <v>2.8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.5</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.26</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45958.41666666666</v>
+        <v>45958.375</v>
       </c>
     </row>
     <row r="4">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,86 +1056,86 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
         <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.22</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.5</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>1.5</v>
       </c>
-      <c r="X5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AD5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45958.45833333334</v>
+        <v>45958.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
         <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="X8" t="n">
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="R9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.52</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA10" t="n">
         <v>3.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3</v>
       </c>
       <c r="AB10" t="n">
         <v>1.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.33</v>
+        <v>2.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.22</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>3.08</v>
+        <v>4.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AA12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.9</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.43</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.38</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.73</v>
+        <v>2.73</v>
       </c>
       <c r="M14" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>1.97</v>
+        <v>2.43</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="T14" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.74</v>
+        <v>1.94</v>
       </c>
       <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z16" t="n">
         <v>2.02</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="AA16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.34</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.46</v>
+        <v>1.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>5.27</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>2.44</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>5.84</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.56</v>
+        <v>2.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.44</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>2.54</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.21</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.23</v>
+        <v>2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.63</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W19" t="n">
         <v>1.36</v>
       </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" t="n">
         <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.82</v>
+        <v>4.23</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.58</v>
+        <v>1.96</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X20" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.29</v>
+        <v>3.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X21" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.8</v>
+        <v>4.03</v>
       </c>
       <c r="AB21" t="n">
         <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,58 +3249,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
         <v>3</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T22" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
         <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
         <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.3</v>
+        <v>4.29</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD22" t="n">
         <v>1.85</v>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.44</v>
+        <v>3.02</v>
       </c>
       <c r="U23" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.22</v>
       </c>
-      <c r="X23" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.34</v>
       </c>
-      <c r="M24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>7</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>3.6</v>
+        <v>1.78</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA26" t="n">
         <v>2.88</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="AB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.3</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA28" t="n">
         <v>3.4</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="AB28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.82</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.36</v>
+        <v>3.59</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.21</v>
+        <v>2.77</v>
       </c>
       <c r="T30" t="n">
-        <v>2.64</v>
+        <v>2.85</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4539,16 +4539,16 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="O32" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P32" t="n">
         <v>2.25</v>
@@ -4560,40 +4560,40 @@
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
         <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4612,13 +4612,142 @@
         <v>1.44</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45958.82291666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45958.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="M2" t="n">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="M3" t="n">
         <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.73</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
         <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X3" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45958.375</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>2.24</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>3.52</v>
+        <v>2.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>2.34</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.56</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.17</v>
+        <v>1.46</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>3.52</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>4.6</v>
+        <v>2.38</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.49</v>
+        <v>2.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>1.41</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>4.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,13 +1126,13 @@
         <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1314,49 +1314,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="O7" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
         <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
         <v>3.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AA7" t="n">
         <v>3.5</v>
@@ -1368,7 +1368,7 @@
         <v>2.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.46</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.55</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
         <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.93</v>
+        <v>1.34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>3.97</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="U9" t="n">
         <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AB9" t="n">
         <v>1.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH9" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="O10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.9</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.07</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.3</v>
+        <v>3.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>2.89</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.91</v>
       </c>
       <c r="O11" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.29</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AC11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.57</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AI11" t="n">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>3.51</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X12" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2097,34 +2097,34 @@
         <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
         <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
         <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Y13" t="n">
         <v>1.72</v>
@@ -2133,16 +2133,16 @@
         <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" t="n">
         <v>1.85</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N14" t="n">
-        <v>2.43</v>
+        <v>3.74</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
         <v>1.29</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>3.41</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
         <v>1.85</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.8</v>
+        <v>2.36</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>4.1</v>
+        <v>3.19</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.33</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.25</v>
       </c>
-      <c r="X16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.92</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.6</v>
+        <v>1.98</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.54</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.27</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>5.84</v>
+        <v>3.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.57</v>
+        <v>1.83</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="M18" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
         <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
         <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X18" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI18" t="n">
         <v>2</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="O19" t="n">
-        <v>2.88</v>
+        <v>3.62</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.3</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.23</v>
+        <v>3.47</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X20" t="n">
         <v>3.1</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB20" t="n">
         <v>1.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.33</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI20" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.1</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.15</v>
+        <v>5.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.19</v>
+        <v>1.47</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.69</v>
+        <v>2.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.22</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="N22" t="n">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y22" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.13</v>
-      </c>
       <c r="Z22" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.29</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
-        <v>2.6</v>
+        <v>4.02</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
         <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.84</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.86</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,13 +3448,13 @@
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.73</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="N24" t="n">
-        <v>1.97</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>3.13</v>
+        <v>4.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.54</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>4.01</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.26</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AH26" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>3.01</v>
       </c>
       <c r="O30" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.85</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AB30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.36</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI31" t="n">
         <v>1.9</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4539,34 +4539,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.68</v>
+        <v>2.37</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="O32" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
@@ -4575,25 +4575,25 @@
         <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA32" t="n">
         <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>2</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>7.39</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1.75</v>
@@ -1200,46 +1200,46 @@
         <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AC6" t="n">
         <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AI6" t="n">
         <v>1.33</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.44</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="AJ8" t="n">
         <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.97</v>
+        <v>1.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.59</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.16</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.8</v>
+        <v>2.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="M10" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.01</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
-        <v>2.75</v>
+        <v>4.02</v>
       </c>
       <c r="P10" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
         <v>2.9</v>
@@ -1731,31 +1731,31 @@
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>2.89</v>
+        <v>3.23</v>
       </c>
       <c r="N11" t="n">
-        <v>2.91</v>
+        <v>3.74</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.3</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
         <v>1.29</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.51</v>
+        <v>2.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
         <v>3</v>
@@ -1989,31 +1989,31 @@
         <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.29</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AC12" t="n">
         <v>1.92</v>
       </c>
-      <c r="Z12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" t="n">
         <v>3.1</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.5</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>3.74</v>
+        <v>3.51</v>
       </c>
       <c r="O14" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.3</v>
       </c>
-      <c r="X14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>1.29</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.8</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.63</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.36</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
         <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>1.81</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,28 +2604,28 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.18</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.23</v>
-      </c>
       <c r="Q17" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
         <v>2.9</v>
@@ -2634,31 +2634,31 @@
         <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AB17" t="n">
         <v>1.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.01</v>
+        <v>2.31</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="P18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.7</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>2.61</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="AB19" t="n">
         <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.72</v>
+        <v>2.08</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.47</v>
+        <v>1.39</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.45</v>
+        <v>5.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.38</v>
+        <v>1.34</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.78</v>
+        <v>3.6</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="M21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X21" t="n">
         <v>4</v>
       </c>
-      <c r="N21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="Y21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z21" t="n">
         <v>2.1</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AA21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.62</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>3.97</v>
       </c>
       <c r="M22" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="U22" t="n">
         <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Z22" t="n">
         <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AB22" t="n">
         <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,13 +3319,13 @@
         <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,28 +3378,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.92</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>3.01</v>
       </c>
       <c r="O23" t="n">
-        <v>4.02</v>
+        <v>2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
         <v>2.9</v>
@@ -3408,31 +3408,31 @@
         <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X23" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,13 +3448,13 @@
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>2.53</v>
       </c>
       <c r="M24" t="n">
-        <v>3.59</v>
+        <v>2.92</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>3.01</v>
       </c>
       <c r="O24" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>4.3</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
         <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="O26" t="n">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="P26" t="n">
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.01</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.36</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
         <v>1.65</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="M29" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.3</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X29" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.1</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X30" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.85</v>
+        <v>3.13</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4619,135 +4619,6 @@
       </c>
       <c r="AK32" s="3" t="n">
         <v>45958.82291666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>45958</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Portugal LigaPro</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Felgueiras 1932</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Farense</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="n">
-        <v>45958.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK32"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,30 +652,30 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
         <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -727,12 +727,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51', '58', '76']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14']</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -794,65 +794,65 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y3" t="n">
         <v>2.75</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.37</v>
-      </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AI3" t="n">
         <v>2</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="P4" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="T4" t="n">
-        <v>2.25</v>
+        <v>3.72</v>
       </c>
       <c r="U4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.45</v>
+        <v>5.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.46</v>
+        <v>2.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O5" t="n">
         <v>2.8</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.87</v>
-      </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>3.52</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="X5" t="n">
-        <v>2.38</v>
+        <v>4.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.52</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.41</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.9</v>
+        <v>2.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1326,7 +1326,7 @@
         <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -1347,10 +1347,10 @@
         <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
         <v>1.98</v>
@@ -1359,16 +1359,16 @@
         <v>1.77</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9</v>
+        <v>2.76</v>
       </c>
       <c r="P8" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.22</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.1</v>
       </c>
-      <c r="U8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AA8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>2.62</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>3.59</v>
+        <v>3.23</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="O9" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="P9" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
-        <v>4.3</v>
+        <v>2.94</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33</v>
+        <v>3.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>4.02</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
         <v>2.9</v>
@@ -1731,31 +1731,31 @@
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>3.23</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.74</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,58 +1959,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="M12" t="n">
-        <v>3.06</v>
+        <v>3.23</v>
       </c>
       <c r="N12" t="n">
-        <v>2.79</v>
+        <v>3.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.64</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X12" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD12" t="n">
         <v>1.91</v>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,34 +2088,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="O13" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
@@ -2124,25 +2124,25 @@
         <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
         <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,55 +2217,55 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.51</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>2.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
         <v>2.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AC14" t="n">
         <v>1.85</v>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.37</v>
+        <v>1.78</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="X15" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,37 +2475,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="N16" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
         <v>1.36</v>
@@ -2514,22 +2514,22 @@
         <v>2.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.8</v>
+        <v>4.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,55 +2604,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.47</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.9</v>
+        <v>3.51</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.45</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.4</v>
+        <v>4.11</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
         <v>1.85</v>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="N18" t="n">
-        <v>2.31</v>
+        <v>2.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.4</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,43 +2862,43 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="O19" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X19" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="Y19" t="n">
         <v>2.05</v>
@@ -2907,13 +2907,13 @@
         <v>1.77</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AB19" t="n">
         <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="AD19" t="n">
         <v>1.75</v>
@@ -2932,13 +2932,13 @@
         <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>2.53</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="N20" t="n">
-        <v>6.4</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.73</v>
+        <v>1.84</v>
       </c>
       <c r="P21" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.66</v>
       </c>
       <c r="T21" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.59</v>
+        <v>2.84</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.97</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
         <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.4</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X22" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,13 +3319,13 @@
         <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>3.97</v>
       </c>
       <c r="M23" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.01</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="R23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
         <v>1.4</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="X23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.31</v>
       </c>
-      <c r="X23" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z23" t="n">
+      <c r="AH23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.53</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>2.92</v>
+        <v>3.59</v>
       </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="T26" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X26" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AB26" t="n">
         <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
         <v>3.21</v>
       </c>
       <c r="N28" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
         <v>1.65</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,43 +4152,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="M29" t="n">
         <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
-        <v>3.03</v>
+        <v>2.82</v>
       </c>
       <c r="P29" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
       <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.36</v>
       </c>
       <c r="V29" t="n">
         <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="Y29" t="n">
         <v>1.9</v>
@@ -4197,16 +4197,16 @@
         <v>1.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AB29" t="n">
         <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="O30" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X30" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4551,22 +4551,22 @@
         <v>3.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
         <v>3.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
@@ -4575,7 +4575,7 @@
         <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="Y32" t="n">
         <v>1.65</v>
@@ -4587,13 +4587,13 @@
         <v>2.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC32" t="n">
         <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AI32" t="n">
         <v>2</v>
@@ -4619,6 +4619,135 @@
       </c>
       <c r="AK32" s="3" t="n">
         <v>45958.82291666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Felgueiras 1932</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Farense</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45958.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>2.42</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.4</v>
+        <v>3.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>2.04</v>
+        <v>3.35</v>
       </c>
       <c r="T4" t="n">
-        <v>3.72</v>
+        <v>2.13</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>2.24</v>
+        <v>4.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.69</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '49']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,65 +1052,65 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="P5" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>2.04</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>3.72</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>4.6</v>
+        <v>2.24</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>2.69</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>5.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.46</v>
+        <v>2.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45958.41666666666</v>
@@ -1185,25 +1185,25 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="N6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
         <v>3.5</v>
@@ -1212,7 +1212,7 @@
         <v>2.17</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
         <v>1.03</v>
@@ -1221,25 +1221,25 @@
         <v>1.14</v>
       </c>
       <c r="X6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AC6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="AI6" t="n">
         <v>1.33</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.15</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.76</v>
+        <v>2.02</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
         <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.22</v>
       </c>
-      <c r="X8" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45958.6875</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="M9" t="n">
-        <v>3.23</v>
+        <v>2.89</v>
       </c>
       <c r="N9" t="n">
-        <v>3.74</v>
+        <v>2.91</v>
       </c>
       <c r="O9" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AH9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.18</v>
+        <v>2.92</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T10" t="n">
         <v>2.9</v>
@@ -1731,31 +1731,31 @@
         <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.06</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>2.79</v>
       </c>
       <c r="O11" t="n">
-        <v>2.02</v>
+        <v>3.56</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>2.39</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X11" t="n">
-        <v>3.85</v>
+        <v>2.55</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.92</v>
       </c>
-      <c r="AA11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="M12" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
         <v>2.9</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X12" t="n">
         <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,13 +2029,13 @@
         <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="M13" t="n">
         <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
         <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
         <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
         <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.78</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.78</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.21</v>
+        <v>3.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="N15" t="n">
-        <v>3.41</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>3.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
         <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD15" t="n">
         <v>1.8</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.81</v>
+        <v>2.35</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="M16" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
         <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.31</v>
+        <v>3.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.93</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,13 +2545,13 @@
         <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="O17" t="n">
         <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
         <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
         <v>2.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45958.6875</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="M18" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
         <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>2.57</v>
+        <v>2.71</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="O19" t="n">
-        <v>3.56</v>
+        <v>2.76</v>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.53</v>
+        <v>2.09</v>
       </c>
       <c r="M20" t="n">
-        <v>2.92</v>
+        <v>3.23</v>
       </c>
       <c r="N20" t="n">
         <v>3.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
         <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="X20" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.54</v>
+        <v>3.47</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.84</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.1</v>
+        <v>2.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3.66</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
-        <v>5.75</v>
+        <v>2.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.84</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.62</v>
+        <v>1.78</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>1.54</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.31</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.62</v>
+        <v>1.84</v>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>3.66</v>
       </c>
       <c r="T22" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>3.18</v>
+        <v>5.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>2.84</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.9</v>
+        <v>2.62</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.97</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
         <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="O23" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="T23" t="n">
-        <v>3.43</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="X23" t="n">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3448,13 +3448,13 @@
         <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>2.18</v>
       </c>
       <c r="M24" t="n">
-        <v>3.59</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="X24" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.63</v>
+        <v>1.97</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>3.45</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.97</v>
+        <v>2.72</v>
       </c>
       <c r="M26" t="n">
         <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.7</v>
+        <v>2.51</v>
       </c>
       <c r="O26" t="n">
-        <v>2.57</v>
+        <v>3.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.13</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>2.51</v>
+        <v>3.01</v>
       </c>
       <c r="O27" t="n">
-        <v>3.28</v>
+        <v>2.69</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>3.66</v>
+        <v>3.44</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="M28" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.01</v>
+        <v>3.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="T28" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="X28" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,43 +4281,43 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="M30" t="n">
         <v>3.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>3.06</v>
+        <v>2.82</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.21</v>
+        <v>3.99</v>
       </c>
       <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.36</v>
       </c>
       <c r="V30" t="n">
         <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="Y30" t="n">
         <v>1.9</v>
@@ -4326,16 +4326,16 @@
         <v>1.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="AB30" t="n">
         <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>

--- a/jogos_2025-10-28.xlsx
+++ b/jogos_2025-10-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK33"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,112 +1159,112 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['38', '40', '57']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45958.54166666666</v>
+        <v>45958.5</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,112 +1288,112 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.7</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>1.77</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.86</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58', '67']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>2.62</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45958.60416666666</v>
+        <v>45958.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1439,90 +1439,90 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>6.4</v>
+        <v>1.55</v>
       </c>
       <c r="O8" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.8</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.44</v>
       </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AK8" s="3" t="n">
-        <v>45958.6875</v>
+        <v>45958.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>2.89</v>
+        <v>5.5</v>
       </c>
       <c r="N9" t="n">
-        <v>2.91</v>
+        <v>8.27</v>
       </c>
       <c r="O9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['20', '36', '82']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH9" t="n">
         <v>3</v>
       </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI9" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45958.6875</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>2.81</v>
       </c>
       <c r="P10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AC10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['9', '42', '45+3']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['5', '89']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.85</v>
       </c>
-      <c r="AD10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45958.6875</v>
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>3.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.79</v>
+        <v>1.99</v>
       </c>
       <c r="O11" t="n">
-        <v>3.56</v>
+        <v>4.13</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
         <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X11" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '34']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '28', '32', '43', '47', '90+2']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45958.6875</v>
@@ -1933,91 +1933,91 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.03</v>
+        <v>3.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>4.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="n">
         <v>4.2</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2029,13 +2029,13 @@
         <v>1.33</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45958.6875</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.86</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.43</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.44</v>
+        <v>3.29</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.36</v>
       </c>
-      <c r="X13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '53', '89']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>2.66</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>1.34</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45958.6875</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,19 +2191,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2213,87 +2213,87 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.25</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.9</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45958.6875</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2342,87 +2342,87 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4.4</v>
+        <v>2.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.56</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.33</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.35</v>
-      </c>
       <c r="X15" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77', '90+2']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45958.6875</v>
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="M16" t="n">
         <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.62</v>
+        <v>4.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
         <v>1.85</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.36</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI16" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45958.6875</v>
@@ -2587,20 +2587,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '58', '77', '80']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.35</v>
+        <v>3.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q18" t="n">
         <v>3</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.7</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>2.71</v>
+        <v>3.32</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AG18" t="n">
         <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45958.6875</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="N19" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
-        <v>3.82</v>
+        <v>2.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.72</v>
+        <v>2.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.64</v>
+        <v>4.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>['16', '90+4']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45958.6875</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="M20" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>2.41</v>
       </c>
       <c r="O20" t="n">
-        <v>2.75</v>
+        <v>3.62</v>
       </c>
       <c r="P20" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.92</v>
+        <v>3.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45958.6875</v>
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.47</v>
+        <v>2.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.55</v>
+        <v>3.64</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
+          <t>['9', '61', '66']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45958.6875</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.84</v>
+        <v>2.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>3.86</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.66</v>
+        <v>3.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>5.75</v>
+        <v>4.55</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['2', '11', '41', '44', '48', '79']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.15</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>2.84</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45958.6875</v>
@@ -3352,109 +3352,109 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="M23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T23" t="n">
         <v>3.15</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45958.6875</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['39', '50', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.36</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45958.6875</v>
@@ -3595,127 +3595,127 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '53']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45958.69791666666</v>
+        <v>45958.6875</v>
       </c>
     </row>
     <row r="26">
@@ -3729,119 +3729,119 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '61', '90+2']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '90+5']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3858,29 +3858,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3890,87 +3890,87 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['105']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45958.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,109 +3997,109 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.97</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2.57</v>
+        <v>3.19</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X28" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4116,119 +4116,119 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
+          <t>['6', '84']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4277,32 +4277,32 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="P30" t="n">
         <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.99</v>
+        <v>3.54</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
         <v>2.75</v>
@@ -4317,25 +4317,25 @@
         <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
         <v>1.65</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="O31" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="R31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.36</v>
       </c>
       <c r="V31" t="n">
         <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X31" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA31" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG31" t="n">
         <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45958.69791666666</v>
@@ -4498,127 +4498,127 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="M32" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="P32" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.97</v>
+        <v>3.85</v>
       </c>
       <c r="R32" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="T32" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
         <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X32" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['56', '83']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '38']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="AI32" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45958.82291666666</v>
+        <v>45958.69791666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,126 +4627,255 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK33" s="3" t="n">
+        <v>45958.82291666666</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Portugal LigaPro</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Felgueiras 1932</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Farense</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" s="3" t="n">
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
         <v>45958.875</v>
       </c>
     </row>
